--- a/JsonConverter/ExcelFiles/DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/DialogueGroup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F905D8-47EC-46C4-B0C9-0E8899EA7784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339A734D-F5AB-4D60-BB01-394B65CBD0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9390" yWindow="990" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>DialogueIdList</t>
-  </si>
-  <si>
-    <t>메인스트림 1_1챕터 그룹</t>
-  </si>
-  <si>
-    <t>dialogue_mainstream_1_1_100,dialogue_mainstream_1_1_200.dialogue_mainstream_1_1_300</t>
   </si>
   <si>
     <t>string[]</t>
@@ -60,6 +54,14 @@
   </si>
   <si>
     <t>dialogue_group_chapter1_1_4</t>
+  </si>
+  <si>
+    <t>챕터1 클리어 대사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter01_1,dialogue_chapter01_2,dialogue_chapter01_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -412,28 +414,28 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -441,32 +443,32 @@
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/JsonConverter/ExcelFiles/DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/DialogueGroup.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339A734D-F5AB-4D60-BB01-394B65CBD0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455F027A-7398-480D-B6E1-A52E4B47003E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12060" yWindow="990" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>DialogueIdList</t>
   </si>
@@ -43,25 +43,90 @@
     <t>string</t>
   </si>
   <si>
-    <t>dialogue_group_chapter1_1_1</t>
+    <t>dialogue_group_chapter1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>dialogue_group_chapter1_1_2</t>
-  </si>
-  <si>
-    <t>dialogue_group_chapter1_1_3</t>
-  </si>
-  <si>
-    <t>dialogue_group_chapter1_1_4</t>
-  </si>
-  <si>
-    <t>챕터1 클리어 대사</t>
+    <t>dialogue_group_chapter2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>dialogue_chapter01_1,dialogue_chapter01_2,dialogue_chapter01_3</t>
+    <t>dialogue_group_chapter3</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter5</t>
+  </si>
+  <si>
+    <t>dialogue_group_chapter6</t>
+  </si>
+  <si>
+    <t>dialogue_group_chapter7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter01_1,dialogue_chapter01_2,dialogue_chapter01_3,dialogue_chapter01_4,dialogue_chapter01_5,dialogue_chapter01_6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter02_1,dialogue_chapter02_2,dialogue_chapter02_3,dialogue_chapter02_4,dialogue_chapter02_5,dialogue_chapter02_6,dialogue_chapter02_7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter03_1,dialogue_chapter03_2,dialogue_chapter03_3,dialogue_chapter03_4,dialogue_chapter03_5,dialogue_chapter03_6,dialogue_chapter03_7,dialogue_chapter03_8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter04_1,dialogue_chapter04_2,dialogue_chapter04_3,dialogue_chapter04_4,dialogue_chapter04_5,dialogue_chapter04_6,dialogue_chapter04_7,dialogue_chapter04_8,dialogue_chapter04_9,dialogue_chapter04_10,dialogue_chapter04_11,dialogue_chapter04_12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter05_1,dialogue_chapter05_2,dialogue_chapter05_3,dialogue_chapter05_4,dialogue_chapter05_5,dialogue_chapter05_6,dialogue_chapter05_7,dialogue_chapter05_8,dialogue_chapter05_9,dialogue_chapter05_10,dialogue_chapter05_11,dialogue_chapter05_12,dialogue_chapter05_13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter07_1,dialogue_chapter07_2,dialogue_chapter07_3,dialogue_chapter07_4,dialogue_chapter07_5,dialogue_chapter07_6,dialogue_chapter07_7,dialogue_chapter07_8,dialogue_chapter07_9,dialogue_chapter07_10,dialogue_chapter07_11,dialogue_chapter07_12,dialogue_chapter07_13,dialogue_chapter07_14,dialogue_chapter07_15,dialogue_chapter07_16,dialogue_chapter07_17</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter06_1,dialogue_chapter06_2,dialogue_chapter06_3,dialogue_chapter06_4,dialogue_chapter06_5,dialogue_chapter06_6,dialogue_chapter06_7,dialogue_chapter06_8,dialogue_chapter06_9,dialogue_chapter06_10,dialogue_chapter06_11,dialogue_chapter06_12,dialogue_chapter06_13,dialogue_chapter06_14,dialogue_chapter06_15,dialogue_chapter06_16,dialogue_chapter06_17,dialogue_chapter06_18</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_final</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터7 클리어 대사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터2</t>
+  </si>
+  <si>
+    <t>챕터3</t>
+  </si>
+  <si>
+    <t>챕터4</t>
+  </si>
+  <si>
+    <t>챕터5</t>
+  </si>
+  <si>
+    <t>챕터6</t>
+  </si>
+  <si>
+    <t>챕터7</t>
+  </si>
+  <si>
+    <t>dialogue_final_1,dialogue_final_2,dialogue_final_3,dialogue_final_4,dialogue_final_5,dialogue_final_6,dialogue_final_7,dialogue_final_8,dialogue_final_9,dialogue_final_10,dialogue_final_11,dialogue_final_12,dialogue_final_13,dialogue_final_14,dialogue_final_15,dialogue_final_16,dialogue_final_17,dialogue_final_18,dialogue_final_19,dialogue_final_20,dialogue_final_21,dialogue_final_22,dialogue_final_23,dialogue_final_24,dialogue_final_25,dialogue_final_26,dialogue_final_26,dialogue_final_27,dialogue_final_28,dialogue_final_29,dialogue_final_30,dialogue_final_31,dialogue_final_32,dialogue_final_33,dialogue_final_34,dialogue_final_35,dialogue_final_36,dialogue_final_37,dialogue_final_38,dialogue_final_39,dialogue_final_40,dialogue_final_41,dialogue_final_42,dialogue_final_43,dialogue_final_44,dialogue_final_45</t>
   </si>
 </sst>
 </file>
@@ -162,7 +227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -171,9 +236,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -446,57 +508,93 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="A11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
@@ -504,114 +602,114 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/DialogueGroup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455F027A-7398-480D-B6E1-A52E4B47003E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8995280E-A995-4101-8BAB-3EC9331063F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12060" yWindow="990" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="0" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/DialogueGroup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8995280E-A995-4101-8BAB-3EC9331063F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2710A5-B27C-49FA-91A7-C38A23792F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="0" windowWidth="28770" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12210" yWindow="1230" windowWidth="23325" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>DialogueIdList</t>
   </si>
@@ -43,90 +43,104 @@
     <t>string</t>
   </si>
   <si>
-    <t>dialogue_group_chapter1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_group_chapter2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_group_chapter3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_group_chapter4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_group_chapter5</t>
-  </si>
-  <si>
-    <t>dialogue_group_chapter6</t>
-  </si>
-  <si>
-    <t>dialogue_group_chapter7</t>
-  </si>
-  <si>
-    <t>dialogue_chapter01_1,dialogue_chapter01_2,dialogue_chapter01_3,dialogue_chapter01_4,dialogue_chapter01_5,dialogue_chapter01_6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter02_1,dialogue_chapter02_2,dialogue_chapter02_3,dialogue_chapter02_4,dialogue_chapter02_5,dialogue_chapter02_6,dialogue_chapter02_7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter03_1,dialogue_chapter03_2,dialogue_chapter03_3,dialogue_chapter03_4,dialogue_chapter03_5,dialogue_chapter03_6,dialogue_chapter03_7,dialogue_chapter03_8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter04_1,dialogue_chapter04_2,dialogue_chapter04_3,dialogue_chapter04_4,dialogue_chapter04_5,dialogue_chapter04_6,dialogue_chapter04_7,dialogue_chapter04_8,dialogue_chapter04_9,dialogue_chapter04_10,dialogue_chapter04_11,dialogue_chapter04_12</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter05_1,dialogue_chapter05_2,dialogue_chapter05_3,dialogue_chapter05_4,dialogue_chapter05_5,dialogue_chapter05_6,dialogue_chapter05_7,dialogue_chapter05_8,dialogue_chapter05_9,dialogue_chapter05_10,dialogue_chapter05_11,dialogue_chapter05_12,dialogue_chapter05_13</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter07_1,dialogue_chapter07_2,dialogue_chapter07_3,dialogue_chapter07_4,dialogue_chapter07_5,dialogue_chapter07_6,dialogue_chapter07_7,dialogue_chapter07_8,dialogue_chapter07_9,dialogue_chapter07_10,dialogue_chapter07_11,dialogue_chapter07_12,dialogue_chapter07_13,dialogue_chapter07_14,dialogue_chapter07_15,dialogue_chapter07_16,dialogue_chapter07_17</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_chapter06_1,dialogue_chapter06_2,dialogue_chapter06_3,dialogue_chapter06_4,dialogue_chapter06_5,dialogue_chapter06_6,dialogue_chapter06_7,dialogue_chapter06_8,dialogue_chapter06_9,dialogue_chapter06_10,dialogue_chapter06_11,dialogue_chapter06_12,dialogue_chapter06_13,dialogue_chapter06_14,dialogue_chapter06_15,dialogue_chapter06_16,dialogue_chapter06_17,dialogue_chapter06_18</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_group_final</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터7 클리어 대사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>챕터2</t>
-  </si>
-  <si>
-    <t>챕터3</t>
-  </si>
-  <si>
-    <t>챕터4</t>
-  </si>
-  <si>
-    <t>챕터5</t>
-  </si>
-  <si>
-    <t>챕터6</t>
-  </si>
-  <si>
-    <t>챕터7</t>
-  </si>
-  <si>
-    <t>dialogue_final_1,dialogue_final_2,dialogue_final_3,dialogue_final_4,dialogue_final_5,dialogue_final_6,dialogue_final_7,dialogue_final_8,dialogue_final_9,dialogue_final_10,dialogue_final_11,dialogue_final_12,dialogue_final_13,dialogue_final_14,dialogue_final_15,dialogue_final_16,dialogue_final_17,dialogue_final_18,dialogue_final_19,dialogue_final_20,dialogue_final_21,dialogue_final_22,dialogue_final_23,dialogue_final_24,dialogue_final_25,dialogue_final_26,dialogue_final_26,dialogue_final_27,dialogue_final_28,dialogue_final_29,dialogue_final_30,dialogue_final_31,dialogue_final_32,dialogue_final_33,dialogue_final_34,dialogue_final_35,dialogue_final_36,dialogue_final_37,dialogue_final_38,dialogue_final_39,dialogue_final_40,dialogue_final_41,dialogue_final_42,dialogue_final_43,dialogue_final_44,dialogue_final_45</t>
+    <t>dialogue_group_chapter07_end</t>
+  </si>
+  <si>
+    <t>dialogue_group_chapter07_start</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터7 시작</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터7 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter01_end_1,dialogue_chapter01_end_2,dialogue_chapter01_end_3,dialogue_chapter01_end_4,dialogue_chapter01_end_5,dialogue_chapter01_end_6</t>
+  </si>
+  <si>
+    <t>dialogue_chapter02_end_1,dialogue_chapter02_end_2,dialogue_chapter02_end_3,dialogue_chapter02_end_4,dialogue_chapter02_end_5,dialogue_chapter02_end_6,dialogue_chapter02_end_7</t>
+  </si>
+  <si>
+    <t>dialogue_chapter03_end_1,dialogue_chapter03_end_2,dialogue_chapter03_end_3,dialogue_chapter03_end_4,dialogue_chapter03_end_5,dialogue_chapter03_end_6,dialogue_chapter03_end_7,dialogue_chapter03_end_8</t>
+  </si>
+  <si>
+    <t>dialogue_chapter04_end_1,dialogue_chapter04_end_2,dialogue_chapter04_end_3,dialogue_chapter04_end_4,dialogue_chapter04_end_5,dialogue_chapter04_end_6,dialogue_chapter04_end_7,dialogue_chapter04_end_8,dialogue_chapter04_end_9,dialogue_chapter04_end_10,dialogue_chapter04_end_11,dialogue_chapter04_end_12</t>
+  </si>
+  <si>
+    <t>dialogue_chapter05_end_1,dialogue_chapter05_end_2,dialogue_chapter05_end_3,dialogue_chapter05_end_4,dialogue_chapter05_end_5,dialogue_chapter05_end_6,dialogue_chapter05_end_7,dialogue_chapter05_end_8,dialogue_chapter05_end_9,dialogue_chapter05_end_10,dialogue_chapter05_end_11,dialogue_chapter05_end_12,dialogue_chapter05_end_13</t>
+  </si>
+  <si>
+    <t>dialogue_group_chapter01_end</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter02_end</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter03_end</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter04_end</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter05_end</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter06_start</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터1 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터2 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터3 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터4 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터5 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터6 시작</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_group_chapter06_end</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>챕터6 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter06_start_1,dialogue_chapter06_start_2,dialogue_chapter06_start_3,dialogue_chapter06_start_4,dialogue_chapter06_start_5,dialogue_chapter06_start_6,dialogue_chapter06_start_7,dialogue_chapter06_start_8,dialogue_chapter06_start_9,dialogue_chapter06_start_10,dialogue_chapter06_start_11,dialogue_chapter06_start_12,dialogue_chapter06_start_13,dialogue_chapter06_start_14,dialogue_chapter06_start_15,dialogue_chapter06_start_16,dialogue_chapter06_start_17,dialogue_chapter06_start_18,dialogue_chapter06_start_19,dialogue_chapter06_start_20,dialogue_chapter06_start_21,dialogue_chapter06_start_22</t>
+  </si>
+  <si>
+    <t>dialogue_chapter06_end_1,dialogue_chapter06_2,dialogue_chapter06_3,dialogue_chapter06_4,dialogue_chapter06_5,dialogue_chapter06_6,dialogue_chapter06_7,dialogue_chapter06_8,dialogue_chapter06_9,dialogue_chapter06_10,dialogue_chapter06_11,dialogue_chapter06_12,dialogue_chapter06_13</t>
+  </si>
+  <si>
+    <t>dialogue_chapter07_start_1,dialogue_chapter07_start_2,dialogue_chapter07_start_3,dialogue_chapter07_start_4,dialogue_chapter07_start_5,dialogue_chapter07_start_6,dialogue_chapter07_start_7,dialogue_chapter07_start_8,dialogue_chapter07_start_9,dialogue_chapter07_start_10,dialogue_chapter07_start_11,dialogue_chapter07_start_12,dialogue_chapter07_start_13,dialogue_chapter07_start_14,dialogue_chapter07_start_15,dialogue_chapter07_start_16,dialogue_chapter07_start_17,dialogue_chapter07_start_18,dialogue_chapter07_start_19,dialogue_chapter07_start_20,dialogue_chapter07_start_21</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_chapter07_end_1,dialogue_chapter07_end_2,dialogue_chapter07_end_3,dialogue_chapter07_end_4,dialogue_chapter07_end_5,dialogue_chapter07_end_6,dialogue_chapter07_end_7,dialogue_chapter07_end_8,dialogue_chapter07_end_9,dialogue_chapter07_end_10,dialogue_chapter07_end_11,dialogue_chapter07_end_12,dialogue_chapter07_end_13,dialogue_chapter07_end_14,dialogue_chapter07_end_15,dialogue_chapter07_end_16,dialogue_chapter07_end_17,dialogue_chapter07_end_18,dialogue_chapter07_end_19,dialogue_chapter07_end_20,dialogue_chapter07_end_21,dialogue_chapter07_end_22,dialogue_chapter07_end_23,dialogue_chapter07_end_24,dialogue_chapter07_end_25,dialogue_chapter07_end_26,dialogue_chapter07_end_26,dialogue_chapter07_end_27,dialogue_chapter07_end_28,dialogue_chapter07_end_29,dialogue_chapter07_end_30,dialogue_chapter07_end_31,dialogue_chapter07_end_32,dialogue_chapter07_end_33,dialogue_chapter07_end_34,dialogue_chapter07_end_35,dialogue_chapter07_end_36,dialogue_chapter07_end_37,dialogue_chapter07_end_38,dialogue_chapter07_end_39,dialogue_chapter07_end_40,dialogue_chapter07_end_41,dialogue_chapter07_end_42,dialogue_chapter07_end_43,dialogue_chapter07_end_44,dialogue_chapter07_end_45</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -465,7 +479,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C1000"/>
+  <dimension ref="A1:C1001"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32.28515625" customWidth="1"/>
@@ -505,106 +519,112 @@
     </row>
     <row r="4" spans="1:3" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>30</v>
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1">
       <c r="A15" s="5"/>
@@ -612,9 +632,9 @@
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
       <c r="A17" s="6"/>
@@ -662,9 +682,9 @@
       <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
       <c r="A27" s="7"/>
@@ -692,9 +712,9 @@
       <c r="C31" s="7"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
@@ -711,7 +731,11 @@
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+    </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
@@ -1676,6 +1700,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
